--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\EXCEL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6FD734E-FECF-45B3-8E49-D07F3F07D01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9D438-3C7B-4E56-92B7-CA990EE3F81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43C9D438-3C7B-4E56-92B7-CA990EE3F81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C59F1A-205D-4FAF-9301-0406469E9558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C59F1A-205D-4FAF-9301-0406469E9558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A0E9BF-61D8-4FC0-8F64-450ABACF0C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A0E9BF-61D8-4FC0-8F64-450ABACF0C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356B8AC5-4599-437A-ADD7-51C4337A5496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{356B8AC5-4599-437A-ADD7-51C4337A5496}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E50428-F3E4-464D-8989-6464BB404F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E50428-F3E4-464D-8989-6464BB404F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216520E0-9122-4153-BA4E-784F7329B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{216520E0-9122-4153-BA4E-784F7329B2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77C2600-74D7-4EAC-9D51-5CBD9DE4B626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="97">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,6 +52,27 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
+    <t>AHMED</t>
+  </si>
+  <si>
+    <t>Ibrahim</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>Panama</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>01/01/2025</t>
+  </si>
+  <si>
+    <t>01/01/2030</t>
+  </si>
+  <si>
     <t>ABAKAR ADAM</t>
   </si>
   <si>
@@ -70,19 +91,10 @@
     <t>10/09/2024</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>Soudan</t>
   </si>
   <si>
     <t>ADDOUT SOULEMAN</t>
-  </si>
-  <si>
-    <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>M</t>
   </si>
   <si>
     <t xml:space="preserve">AHMED MOHAMED </t>
@@ -870,25 +882,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -896,25 +908,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="10" t="s">
-        <v>15</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -922,25 +934,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="F7" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -954,19 +966,19 @@
         <v>25</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -974,25 +986,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1006,19 +1018,19 @@
         <v>32</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="F10" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1026,13 +1038,13 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>37</v>
@@ -1041,10 +1053,10 @@
         <v>13</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1052,25 +1064,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="D12" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="10" t="s">
-        <v>15</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1078,25 +1090,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1104,25 +1116,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1130,25 +1142,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1156,25 +1168,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1182,25 +1194,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>53</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>15</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>54</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1208,13 +1220,13 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>58</v>
@@ -1223,10 +1235,10 @@
         <v>13</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>59</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1234,25 +1246,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>15</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1260,25 +1272,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1286,25 +1298,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1312,25 +1324,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1338,25 +1350,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1367,22 +1379,22 @@
         <v>73</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1390,25 +1402,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1425,16 +1437,16 @@
         <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>81</v>
+        <v>21</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1451,16 +1463,16 @@
         <v>84</v>
       </c>
       <c r="E27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F27" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="10" t="s">
-        <v>41</v>
-      </c>
       <c r="H27" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1474,19 +1486,19 @@
         <v>87</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>15</v>
+        <v>88</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F28" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1494,38 +1506,52 @@
         <v>26</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>91</v>
+        <v>11</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>92</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A30" s="11">
+      <c r="A30" s="4">
         <v>27</v>
       </c>
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="14"/>
+      <c r="B30" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A31" s="11">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77C2600-74D7-4EAC-9D51-5CBD9DE4B626}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCB19E9-E26F-4C28-B541-ECB3002B3E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\Documents\SAPIEN\PowerShell Studio\Files\ASTI\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCB19E9-E26F-4C28-B541-ECB3002B3E2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF239599-9839-479C-8F89-A8554E8F0BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7995" yWindow="5535" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -52,51 +52,39 @@
     <t>DATE DE FIN</t>
   </si>
   <si>
-    <t>AHMED</t>
+    <t>ABAKAR ADAM</t>
+  </si>
+  <si>
+    <t>Seida</t>
+  </si>
+  <si>
+    <t>01/01/1983</t>
+  </si>
+  <si>
+    <t>Soudan</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
+    <t>ADDOUT SOULEMAN</t>
   </si>
   <si>
     <t>Ibrahim</t>
   </si>
   <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
-    <t>Panama</t>
+    <t>31/12/1899</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>01/01/2025</t>
-  </si>
-  <si>
-    <t>01/01/2030</t>
-  </si>
-  <si>
-    <t>ABAKAR ADAM</t>
-  </si>
-  <si>
-    <t>Seida</t>
-  </si>
-  <si>
-    <t>01/01/1983</t>
-  </si>
-  <si>
-    <t>Soudan du Sud</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>Soudan</t>
-  </si>
-  <si>
-    <t>ADDOUT SOULEMAN</t>
-  </si>
-  <si>
     <t xml:space="preserve">AHMED MOHAMED </t>
   </si>
   <si>
@@ -115,7 +103,7 @@
     <t>Matthew</t>
   </si>
   <si>
-    <t>Nigeria</t>
+    <t>Nigéria</t>
   </si>
   <si>
     <t>ALHAJ</t>
@@ -292,7 +280,7 @@
     <t>27/08/2004</t>
   </si>
   <si>
-    <t>Ethiopie</t>
+    <t>Éthiopie</t>
   </si>
   <si>
     <t>TOLNO</t>
@@ -797,7 +785,7 @@
     <col min="2" max="2" width="13" style="5" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
     <col min="4" max="4" width="11.85546875" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" customWidth="1"/>
     <col min="6" max="6" width="9.140625" style="9" customWidth="1"/>
     <col min="7" max="7" width="15.140625" style="9" customWidth="1"/>
     <col min="8" max="8" width="12.42578125" customWidth="1"/>
@@ -891,16 +879,16 @@
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>20</v>
-      </c>
       <c r="G5" s="10" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -908,25 +896,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F6" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -934,25 +922,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -960,25 +948,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -986,25 +974,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1012,25 +1000,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1038,25 +1026,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1064,25 +1052,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F12" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1090,25 +1078,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C13" s="8" t="s">
         <v>44</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1116,25 +1104,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1142,25 +1130,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>48</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1168,25 +1156,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1194,25 +1182,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1220,25 +1208,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1246,25 +1234,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F19" s="10" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1272,25 +1260,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1298,25 +1286,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1330,19 +1318,19 @@
         <v>70</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1350,25 +1338,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1376,25 +1364,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>22</v>
+        <v>77</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1402,25 +1390,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="F25" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1428,25 +1416,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1454,25 +1442,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>84</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1480,78 +1468,50 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A29" s="4">
+      <c r="A29" s="11">
         <v>26</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
     </row>
     <row r="30" spans="1:8" ht="39.950000000000003" customHeight="1">
-      <c r="A30" s="4">
+      <c r="A30" s="11">
         <v>27</v>
       </c>
-      <c r="B30" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
     </row>
     <row r="31" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A31" s="11">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF239599-9839-479C-8F89-A8554E8F0BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FAD8D-259A-49EE-A0F5-D50DD5E0FC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8685" yWindow="5535" windowWidth="20115" windowHeight="9945" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -77,9 +77,6 @@
   </si>
   <si>
     <t>Ibrahim</t>
-  </si>
-  <si>
-    <t>31/12/1899</t>
   </si>
   <si>
     <t>M</t>
@@ -876,13 +873,13 @@
         <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" s="10" t="s">
         <v>15</v>
@@ -896,13 +893,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="D6" s="10" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -911,7 +908,7 @@
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>15</v>
@@ -922,19 +919,19 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="F7" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>15</v>
@@ -948,22 +945,22 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="10" t="s">
         <v>28</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>29</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>15</v>
@@ -974,19 +971,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="D9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="F9" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>15</v>
@@ -1000,22 +997,22 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="D10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="E10" s="2" t="s">
         <v>36</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>37</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>15</v>
@@ -1026,22 +1023,22 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>40</v>
-      </c>
       <c r="D11" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
@@ -1052,16 +1049,16 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="D12" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
@@ -1078,19 +1075,19 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G13" s="10" t="s">
         <v>15</v>
@@ -1104,19 +1101,19 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="D14" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G14" s="10" t="s">
         <v>15</v>
@@ -1130,22 +1127,22 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="E15" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" s="10" t="s">
         <v>50</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>51</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
@@ -1156,19 +1153,19 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="F16" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G16" s="10" t="s">
         <v>15</v>
@@ -1182,22 +1179,22 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
@@ -1208,19 +1205,19 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="D18" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G18" s="10" t="s">
         <v>15</v>
@@ -1234,16 +1231,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>13</v>
@@ -1260,19 +1257,19 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="8" t="s">
-        <v>66</v>
-      </c>
       <c r="D20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>15</v>
@@ -1286,19 +1283,19 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>68</v>
-      </c>
       <c r="D21" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F21" s="10" t="s">
         <v>18</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>19</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>15</v>
@@ -1312,22 +1309,22 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="D22" s="10" t="s">
         <v>70</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>71</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -1338,19 +1335,19 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>15</v>
@@ -1364,19 +1361,19 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="8" t="s">
+      <c r="D24" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="F24" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>14</v>
@@ -1390,22 +1387,22 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C25" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="D25" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F25" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="10" t="s">
-        <v>81</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -1416,22 +1413,22 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="C26" s="8" t="s">
+      <c r="D26" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="E26" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F26" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -1442,16 +1439,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="C27" s="8" t="s">
+      <c r="D27" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="D27" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>13</v>
@@ -1468,22 +1465,22 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="8" t="s">
+      <c r="D28" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="E28" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F28" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184FAD8D-259A-49EE-A0F5-D50DD5E0FC22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B73F220-3999-40BC-81F1-5C8F9A3636AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="72">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t>01/01/1983</t>
+    <t/>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,12 +67,6 @@
     <t>F</t>
   </si>
   <si>
-    <t>10/09/2024</t>
-  </si>
-  <si>
-    <t>01/01/1900</t>
-  </si>
-  <si>
     <t>ADDOUT SOULEMAN</t>
   </si>
   <si>
@@ -88,12 +82,6 @@
     <t>Monira</t>
   </si>
   <si>
-    <t>01/01/1987</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
     <t>AJAYI</t>
   </si>
   <si>
@@ -109,12 +97,6 @@
     <t>Mudather</t>
   </si>
   <si>
-    <t>08/04/1999</t>
-  </si>
-  <si>
-    <t>25/11/2024</t>
-  </si>
-  <si>
     <t>ANTURIA</t>
   </si>
   <si>
@@ -130,24 +112,15 @@
     <t>Elizandra Maria</t>
   </si>
   <si>
-    <t>12/02/2006</t>
-  </si>
-  <si>
     <t>Angola</t>
   </si>
   <si>
-    <t>09/10/2025</t>
-  </si>
-  <si>
     <t>EBRAHIM DUD</t>
   </si>
   <si>
     <t>Nabil</t>
   </si>
   <si>
-    <t>16/09/2025</t>
-  </si>
-  <si>
     <t>EGBOYE</t>
   </si>
   <si>
@@ -169,15 +142,9 @@
     <t>Gyurme</t>
   </si>
   <si>
-    <t>08/02/1997</t>
-  </si>
-  <si>
     <t>Tibet</t>
   </si>
   <si>
-    <t>08/10/2025</t>
-  </si>
-  <si>
     <t>KHAROT</t>
   </si>
   <si>
@@ -193,15 +160,9 @@
     <t>Ilham</t>
   </si>
   <si>
-    <t>15/08/2002</t>
-  </si>
-  <si>
     <t>Algérie</t>
   </si>
   <si>
-    <t>07/11/2025</t>
-  </si>
-  <si>
     <t>MOUSSA BABAY</t>
   </si>
   <si>
@@ -235,12 +196,6 @@
     <t>Mohammed</t>
   </si>
   <si>
-    <t>01/01/1994</t>
-  </si>
-  <si>
-    <t>17/09/2024</t>
-  </si>
-  <si>
     <t>SALAH</t>
   </si>
   <si>
@@ -250,9 +205,6 @@
     <t>Ahmed</t>
   </si>
   <si>
-    <t>01/01/1998</t>
-  </si>
-  <si>
     <t>Somalie</t>
   </si>
   <si>
@@ -262,21 +214,12 @@
     <t>Nyima</t>
   </si>
   <si>
-    <t>10/06/1997</t>
-  </si>
-  <si>
-    <t>07/10/2025</t>
-  </si>
-  <si>
     <t>TOLA</t>
   </si>
   <si>
     <t>Boja</t>
   </si>
   <si>
-    <t>27/08/2004</t>
-  </si>
-  <si>
     <t>Éthiopie</t>
   </si>
   <si>
@@ -293,9 +236,6 @@
   </si>
   <si>
     <t>Karma</t>
-  </si>
-  <si>
-    <t>15/05/1988</t>
   </si>
   <si>
     <t>Chine</t>
@@ -856,10 +796,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -867,25 +807,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -893,13 +833,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -908,10 +848,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -919,25 +859,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -945,25 +885,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -971,25 +911,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -997,25 +937,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1023,25 +963,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1049,25 +989,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1075,25 +1015,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1101,25 +1041,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1127,25 +1067,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1153,25 +1093,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1179,25 +1119,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1205,25 +1145,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1231,25 +1171,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1257,25 +1197,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1283,25 +1223,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1309,25 +1249,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>71</v>
+        <v>11</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1335,25 +1275,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1361,25 +1301,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1387,25 +1327,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>80</v>
+        <v>11</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1413,25 +1353,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>83</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1439,25 +1379,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1465,25 +1405,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B73F220-3999-40BC-81F1-5C8F9A3636AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF50978B-AC4F-4EAF-B7B7-CF9211236E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Excel/liste_groupe_Samedi.xlsx
+++ b/Excel/liste_groupe_Samedi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yvesb\AppData\Roaming\ASTI\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF50978B-AC4F-4EAF-B7B7-CF9211236E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4114A3D6-F32A-464D-A745-59BDF589C448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>Période de présence aux cours 2025 - 2026 (01/11/2025)</t>
   </si>
@@ -58,7 +58,7 @@
     <t>Seida</t>
   </si>
   <si>
-    <t/>
+    <t>01/01/1983</t>
   </si>
   <si>
     <t>Soudan</t>
@@ -67,6 +67,12 @@
     <t>F</t>
   </si>
   <si>
+    <t>10/09/2024</t>
+  </si>
+  <si>
+    <t>01/01/1900</t>
+  </si>
+  <si>
     <t>ADDOUT SOULEMAN</t>
   </si>
   <si>
@@ -82,6 +88,12 @@
     <t>Monira</t>
   </si>
   <si>
+    <t>01/01/1987</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
     <t>AJAYI</t>
   </si>
   <si>
@@ -97,6 +109,12 @@
     <t>Mudather</t>
   </si>
   <si>
+    <t>08/04/1999</t>
+  </si>
+  <si>
+    <t>25/11/2024</t>
+  </si>
+  <si>
     <t>ANTURIA</t>
   </si>
   <si>
@@ -112,15 +130,24 @@
     <t>Elizandra Maria</t>
   </si>
   <si>
+    <t>12/02/2006</t>
+  </si>
+  <si>
     <t>Angola</t>
   </si>
   <si>
+    <t>09/10/2025</t>
+  </si>
+  <si>
     <t>EBRAHIM DUD</t>
   </si>
   <si>
     <t>Nabil</t>
   </si>
   <si>
+    <t>16/09/2025</t>
+  </si>
+  <si>
     <t>EGBOYE</t>
   </si>
   <si>
@@ -142,9 +169,15 @@
     <t>Gyurme</t>
   </si>
   <si>
+    <t>08/02/1997</t>
+  </si>
+  <si>
     <t>Tibet</t>
   </si>
   <si>
+    <t>08/10/2025</t>
+  </si>
+  <si>
     <t>KHAROT</t>
   </si>
   <si>
@@ -160,9 +193,15 @@
     <t>Ilham</t>
   </si>
   <si>
+    <t>15/08/2002</t>
+  </si>
+  <si>
     <t>Algérie</t>
   </si>
   <si>
+    <t>07/11/2025</t>
+  </si>
+  <si>
     <t>MOUSSA BABAY</t>
   </si>
   <si>
@@ -196,6 +235,12 @@
     <t>Mohammed</t>
   </si>
   <si>
+    <t>01/01/1994</t>
+  </si>
+  <si>
+    <t>17/09/2024</t>
+  </si>
+  <si>
     <t>SALAH</t>
   </si>
   <si>
@@ -205,6 +250,9 @@
     <t>Ahmed</t>
   </si>
   <si>
+    <t>01/01/1998</t>
+  </si>
+  <si>
     <t>Somalie</t>
   </si>
   <si>
@@ -214,12 +262,21 @@
     <t>Nyima</t>
   </si>
   <si>
+    <t>10/06/1997</t>
+  </si>
+  <si>
+    <t>07/10/2025</t>
+  </si>
+  <si>
     <t>TOLA</t>
   </si>
   <si>
     <t>Boja</t>
   </si>
   <si>
+    <t>27/08/2004</t>
+  </si>
+  <si>
     <t>Éthiopie</t>
   </si>
   <si>
@@ -236,6 +293,9 @@
   </si>
   <si>
     <t>Karma</t>
+  </si>
+  <si>
+    <t>15/05/1988</t>
   </si>
   <si>
     <t>Chine</t>
@@ -796,10 +856,10 @@
         <v>13</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -807,25 +867,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -833,13 +893,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>12</v>
@@ -848,10 +908,10 @@
         <v>13</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -859,25 +919,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -885,25 +945,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -911,25 +971,25 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F9" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -937,25 +997,25 @@
         <v>7</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F10" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -963,25 +1023,25 @@
         <v>8</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -989,25 +1049,25 @@
         <v>9</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F12" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1015,25 +1075,25 @@
         <v>10</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1041,25 +1101,25 @@
         <v>11</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1067,25 +1127,25 @@
         <v>12</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1093,25 +1153,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F16" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1119,25 +1179,25 @@
         <v>14</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="F17" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1145,25 +1205,25 @@
         <v>15</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1171,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1197,25 +1257,25 @@
         <v>17</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1223,25 +1283,25 @@
         <v>18</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F21" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1249,25 +1309,25 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F22" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G22" s="10" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1275,25 +1335,25 @@
         <v>20</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F23" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G23" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1301,25 +1361,25 @@
         <v>21</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1327,25 +1387,25 @@
         <v>22</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>61</v>
+        <v>77</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G25" s="10" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1353,25 +1413,25 @@
         <v>23</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1379,25 +1439,25 @@
         <v>24</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="F27" s="10" t="s">
         <v>13</v>
       </c>
       <c r="G27" s="10" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:8" ht="39.950000000000003" customHeight="1">
@@ -1405,25 +1465,25 @@
         <v>25</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="F28" s="10" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G28" s="10" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:8" ht="39.950000000000003" customHeight="1">
